--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91540</v>
+        <v>91543</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96247</v>
+        <v>96252</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92811</v>
+        <v>92816</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91543</v>
+        <v>91546</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96252</v>
+        <v>96255</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92816</v>
+        <v>92819</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91546</v>
+        <v>91553</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96255</v>
+        <v>96265</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92819</v>
+        <v>92826</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91553</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96265</v>
+        <v>96272</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92826</v>
+        <v>92833</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91562</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96272</v>
+        <v>96274</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92833</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91562</v>
+        <v>91560</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96274</v>
+        <v>96300</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92821</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91560</v>
+        <v>91561</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96300</v>
+        <v>96301</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92821</v>
+        <v>92822</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96301</v>
+        <v>96302</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91561</v>
+        <v>91564</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96302</v>
+        <v>96306</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92822</v>
+        <v>92825</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91564</v>
+        <v>91566</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96306</v>
+        <v>96308</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92825</v>
+        <v>92827</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91566</v>
+        <v>91570</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96308</v>
+        <v>96312</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92827</v>
+        <v>92831</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91570</v>
+        <v>91571</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96312</v>
+        <v>96320</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92831</v>
+        <v>92832</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -678,7 +678,7 @@
         <v>129018409</v>
       </c>
       <c r="B2" t="n">
-        <v>91571</v>
+        <v>91574</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -775,7 +775,7 @@
         <v>129018428</v>
       </c>
       <c r="B3" t="n">
-        <v>96320</v>
+        <v>96323</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -872,7 +872,7 @@
         <v>129018426</v>
       </c>
       <c r="B4" t="n">
-        <v>92832</v>
+        <v>92835</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,32 +675,32 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>129018409</v>
+        <v>129018428</v>
       </c>
       <c r="B2" t="n">
-        <v>91574</v>
+        <v>96708</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>5442</v>
+        <v>2180</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
@@ -710,10 +710,10 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>634007</v>
+        <v>633954</v>
       </c>
       <c r="R2" t="n">
-        <v>6552345</v>
+        <v>6552419</v>
       </c>
       <c r="S2" t="n">
         <v>15</v>
@@ -772,32 +772,32 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>129018428</v>
+        <v>129018426</v>
       </c>
       <c r="B3" t="n">
-        <v>96323</v>
+        <v>93197</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E3" t="n">
-        <v>2180</v>
+        <v>4364</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(Fr.:Fr.) P. Karst.</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>633954</v>
+        <v>634002</v>
       </c>
       <c r="R3" t="n">
-        <v>6552419</v>
+        <v>6552286</v>
       </c>
       <c r="S3" t="n">
         <v>15</v>
@@ -869,10 +869,10 @@
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>129018426</v>
+        <v>129018423</v>
       </c>
       <c r="B4" t="n">
-        <v>92835</v>
+        <v>92348</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -880,21 +880,21 @@
         </is>
       </c>
       <c r="E4" t="n">
-        <v>4364</v>
+        <v>5420</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Dropptaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Hydnellum ferrugineum</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>(Fr.:Fr.) P. Karst.</t>
+          <t>(Fr.) Pat.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
@@ -904,10 +904,10 @@
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>634002</v>
+        <v>633935</v>
       </c>
       <c r="R4" t="n">
-        <v>6552286</v>
+        <v>6552423</v>
       </c>
       <c r="S4" t="n">
         <v>15</v>
@@ -963,6 +963,491 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>129018405</v>
+      </c>
+      <c r="B5" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Björsta skans, Srm</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>633949</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6552407</v>
+      </c>
+      <c r="S5" t="n">
+        <v>15</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>129018406</v>
+      </c>
+      <c r="B6" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Björsta skans, Srm</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>633949</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6552375</v>
+      </c>
+      <c r="S6" t="n">
+        <v>15</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>129018408</v>
+      </c>
+      <c r="B7" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Björsta skans, Srm</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>633975</v>
+      </c>
+      <c r="R7" t="n">
+        <v>6552324</v>
+      </c>
+      <c r="S7" t="n">
+        <v>15</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>129018409</v>
+      </c>
+      <c r="B8" t="n">
+        <v>91930</v>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>5442</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Tallticka</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Porodaedalea pini</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Björsta skans, Srm</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>634007</v>
+      </c>
+      <c r="R8" t="n">
+        <v>6552345</v>
+      </c>
+      <c r="S8" t="n">
+        <v>15</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>129018410</v>
+      </c>
+      <c r="B9" t="n">
+        <v>93223</v>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>5448</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Svartvit taggsvamp</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Phellodon melaleucus</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Sw. ex Fr.) P.Karst.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Björsta skans, Srm</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>633948</v>
+      </c>
+      <c r="R9" t="n">
+        <v>6552419</v>
+      </c>
+      <c r="S9" t="n">
+        <v>15</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Södertälje</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Vårdinge</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2025-10-10</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Gustaf Eibl</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 27971-2022 artfynd.xlsx
+++ b/artfynd/A 27971-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -769,6 +774,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018428</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -866,6 +876,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018426</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -963,6 +978,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018423</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1060,6 +1080,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018405</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1157,6 +1182,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018406</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1254,6 +1284,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018408</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1351,6 +1386,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018409</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1448,8 +1488,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129018410</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>